--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/1101-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/1101-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0ADD02BB-0D7E-4E69-A1F9-CA02109136E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{904C2202-A5C0-4BC3-8502-DA319E2C0AFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{2BDFA703-D2D8-46DC-A021-2F1BACE1EC26}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{920CAA53-AF32-4103-AD4C-E2F309B307A1}"/>
   </bookViews>
   <sheets>
     <sheet name="1101-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1616,29 +1616,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{916E0053-9226-40AB-B2CC-B7DB2D8D5301}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{054CC870-FCBE-4A47-B64C-E8F378A8C42D}">
   <dimension ref="A1:X57"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="10.75" customWidth="1"/>
-    <col min="3" max="3" width="9.75" customWidth="1"/>
-    <col min="4" max="4" width="6.25" customWidth="1"/>
-    <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="7" width="6.25" customWidth="1"/>
-    <col min="8" max="8" width="6" customWidth="1"/>
-    <col min="9" max="10" width="6.25" customWidth="1"/>
-    <col min="11" max="13" width="6" customWidth="1"/>
-    <col min="14" max="15" width="6.25" customWidth="1"/>
-    <col min="16" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="6.25" customWidth="1"/>
-    <col min="20" max="20" width="6" customWidth="1"/>
-    <col min="21" max="21" width="6.25" customWidth="1"/>
-    <col min="22" max="22" width="6" customWidth="1"/>
-    <col min="23" max="23" width="6.25" customWidth="1"/>
-    <col min="24" max="24" width="6.875" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1672,7 +1671,7 @@
       <c r="W1" s="30"/>
       <c r="X1" s="22"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1708,7 +1707,7 @@
       <c r="W2" s="32"/>
       <c r="X2" s="33"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1760,7 +1759,7 @@
       </c>
       <c r="X3" s="36"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1828,7 +1827,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="37">
         <v>2024</v>
       </c>
@@ -1900,7 +1899,7 @@
         <v>4.9400000000000004</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="39">
         <v>2023</v>
       </c>
@@ -1972,7 +1971,7 @@
         <v>3.25</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="37">
         <v>2022</v>
       </c>
@@ -2044,7 +2043,7 @@
         <v>1.59</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="39">
         <v>2021</v>
       </c>
@@ -2116,7 +2115,7 @@
         <v>6.71</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="37">
         <v>2020</v>
       </c>
@@ -2188,7 +2187,7 @@
         <v>8.39</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="39">
         <v>2019</v>
       </c>
@@ -2260,7 +2259,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="37">
         <v>2018</v>
       </c>
@@ -2332,7 +2331,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="39">
         <v>2017</v>
       </c>
@@ -2404,7 +2403,7 @@
         <v>7.65</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="37">
         <v>2016</v>
       </c>
@@ -2476,7 +2475,7 @@
         <v>4.3499999999999996</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="39">
         <v>2015</v>
       </c>
@@ -2548,7 +2547,7 @@
         <v>5.23</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="37">
         <v>2014</v>
       </c>
@@ -2620,7 +2619,7 @@
         <v>9.26</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="39">
         <v>2013</v>
       </c>
@@ -2692,7 +2691,7 @@
         <v>5.56</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="37">
         <v>2012</v>
       </c>
@@ -2764,7 +2763,7 @@
         <v>5.63</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="39">
         <v>2011</v>
       </c>
@@ -2836,7 +2835,7 @@
         <v>6.01</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="37">
         <v>2010</v>
       </c>
@@ -2908,7 +2907,7 @@
         <v>6.9</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="39">
         <v>2009</v>
       </c>
@@ -2980,7 +2979,7 @@
         <v>7.32</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="37">
         <v>2008</v>
       </c>
@@ -3052,7 +3051,7 @@
         <v>6.03</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="39">
         <v>2007</v>
       </c>
@@ -3124,7 +3123,7 @@
         <v>14.1</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="37">
         <v>2006</v>
       </c>
@@ -3196,7 +3195,7 @@
         <v>7.23</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="39">
         <v>2005</v>
       </c>
@@ -3268,7 +3267,7 @@
         <v>7.49</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="37">
         <v>2004</v>
       </c>
@@ -3340,7 +3339,7 @@
         <v>6.86</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="39">
         <v>2003</v>
       </c>
@@ -3412,7 +3411,7 @@
         <v>5.2</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="37">
         <v>2002</v>
       </c>
@@ -3484,7 +3483,7 @@
         <v>3.05</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="39">
         <v>2001</v>
       </c>
@@ -3556,7 +3555,7 @@
         <v>2.82</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="37">
         <v>2000</v>
       </c>
@@ -3628,7 +3627,7 @@
         <v>4.29</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="39">
         <v>1999</v>
       </c>
@@ -3700,7 +3699,7 @@
         <v>6.99</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="37">
         <v>1998</v>
       </c>
@@ -3772,7 +3771,7 @@
         <v>6.38</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="41">
         <v>1997</v>
       </c>
@@ -3844,7 +3843,7 @@
         <v>5.77</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="43"/>
       <c r="B33" s="44"/>
       <c r="C33" s="18" t="s">
@@ -3872,7 +3871,7 @@
       <c r="W33" s="50"/>
       <c r="X33" s="46"/>
     </row>
-    <row r="34" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="51">
         <v>1996</v>
       </c>
@@ -3944,7 +3943,7 @@
         <v>3.76</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="53"/>
       <c r="B35" s="54"/>
       <c r="C35" s="20" t="s">
@@ -3972,7 +3971,7 @@
       <c r="W35" s="60"/>
       <c r="X35" s="56"/>
     </row>
-    <row r="36" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="41">
         <v>1995</v>
       </c>
@@ -4044,7 +4043,7 @@
         <v>4.4800000000000004</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="43"/>
       <c r="B37" s="44"/>
       <c r="C37" s="18" t="s">
@@ -4072,7 +4071,7 @@
       <c r="W37" s="50"/>
       <c r="X37" s="46"/>
     </row>
-    <row r="38" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="51">
         <v>1994</v>
       </c>
@@ -4144,7 +4143,7 @@
         <v>7.17</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="53"/>
       <c r="B39" s="54"/>
       <c r="C39" s="20" t="s">
@@ -4172,7 +4171,7 @@
       <c r="W39" s="60"/>
       <c r="X39" s="56"/>
     </row>
-    <row r="40" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="41">
         <v>1993</v>
       </c>
@@ -4244,7 +4243,7 @@
         <v>6.88</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="43"/>
       <c r="B41" s="44"/>
       <c r="C41" s="18" t="s">
@@ -4272,7 +4271,7 @@
       <c r="W41" s="50"/>
       <c r="X41" s="46"/>
     </row>
-    <row r="42" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="51">
         <v>1992</v>
       </c>
@@ -4344,7 +4343,7 @@
         <v>6.19</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="53"/>
       <c r="B43" s="54"/>
       <c r="C43" s="20" t="s">
@@ -4372,7 +4371,7 @@
       <c r="W43" s="60"/>
       <c r="X43" s="56"/>
     </row>
-    <row r="44" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="41">
         <v>1991</v>
       </c>
@@ -4444,7 +4443,7 @@
         <v>6.67</v>
       </c>
     </row>
-    <row r="45" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A45" s="43"/>
       <c r="B45" s="44"/>
       <c r="C45" s="18" t="s">
@@ -4472,7 +4471,7 @@
       <c r="W45" s="50"/>
       <c r="X45" s="46"/>
     </row>
-    <row r="46" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A46" s="51">
         <v>1990</v>
       </c>
@@ -4544,7 +4543,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A47" s="53"/>
       <c r="B47" s="54"/>
       <c r="C47" s="20" t="s">
@@ -4572,7 +4571,7 @@
       <c r="W47" s="60"/>
       <c r="X47" s="56"/>
     </row>
-    <row r="48" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A48" s="41">
         <v>1989</v>
       </c>
@@ -4644,7 +4643,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="49" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A49" s="43"/>
       <c r="B49" s="44"/>
       <c r="C49" s="18" t="s">
@@ -4672,7 +4671,7 @@
       <c r="W49" s="50"/>
       <c r="X49" s="46"/>
     </row>
-    <row r="50" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A50" s="37">
         <v>1988</v>
       </c>
@@ -4744,7 +4743,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="51" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A51" s="39">
         <v>1987</v>
       </c>
@@ -4816,7 +4815,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="52" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A52" s="37">
         <v>1986</v>
       </c>
@@ -4888,7 +4887,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="53" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A53" s="39">
         <v>1985</v>
       </c>
@@ -4960,7 +4959,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="54" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A54" s="37">
         <v>1984</v>
       </c>
@@ -5032,7 +5031,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="55" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A55" s="39">
         <v>1983</v>
       </c>
@@ -5104,7 +5103,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="56" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A56" s="37">
         <v>1981</v>
       </c>
@@ -5176,7 +5175,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="57" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A57" s="39" t="s">
         <v>74</v>
       </c>
